--- a/human_validation/judge/kor/judge_D002_S003_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S003_P002__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,103 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 처리하겠다고 말해 놓은 예정된 회신 전화, 작업지시서, 기본적인 후속 조치들을 계속 잊어버려요. 회사에 일이 다 쌓여 버려서, 승진 기회를 놓칠 수도 있다고 해서 여기로 보내졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 건망증이나 정리정돈 문제를 언제부터 겪기 시작하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 솔직히 초등학교 때부터요. 선생님들이 제가 똑똑하다고 하시면서도, 늘 서류를 잃어버리고, 지시사항의 일부를 놓치고, 수업 과제를 끝내려면 계속 알려줘야 했어요. 이건 지금 이 직장의 압박이 있기 훨씬 전부터 그랬어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 몸이 자주 안절부절못하거나 계속 꼼지락거리고 가만히 앉아 있기 힘든 느낌이 자주 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 안절부절못하거나 가만히 앉아 있지 못한다고 느낀 적은 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 주변에서 일어나는 일들 때문에 쉽게 주의가 흐트러지는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 디지털 작업지시서를 읽다가, 절반쯤 읽었을 때 어떤 소리나 다른 작업 때문에 정신이 팔려요. 그러면 방금 읽은 내용이 뭔지도 모르겠다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)
 인구통계: 성별 여성 / 나이 49 / 직업상태 maintenance or repair worker general / 최종학력 고등학교 졸업
@@ -575,161 +663,40 @@
 증상 지속 기간: 11 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S009
-배경 서술: 아만다가 속한 시설관리 부서는 새로운 운영 관리 업체가 디지털 작업지시서와 에너지 효율 감사, 그리고 그녀가 기대하던 선임 시설관리직 승진과 연계된 한층 엄격한 문서 기준을 도입하면서 큰 변화를 겪었다. 이후 11개월 동안, 오랫동안 의존해 온 손으로 작성한 체크리스트와 물리적인 업무 루틴만으로는 더 이상 충분하지 않았다. 그녀는 여러 단계로 이루어진 서비스 요청 중 집중력을 유지하는 데 어려움을 겪었고, 작업에 필요한 공구와 태블릿을 잃어버렸으며, 예정된 회신 전화를 잊어버리고, 지시사항을 이해했음에도 불구하고 여러 유지보수 업무를 끝맺지 못한 채 남겨두었다. 그 결과로 생긴 업무 적체와 입주민들의 불만, 그리고 아차 사고 이후 진행된 공식 안전 검토는 이 문제를 단순한 직장 내 압박으로 치부할 수 없게 만들었다. 그녀는 오랫동안 노력해 온 승진의 길을 포기하는 대신 평가를 받기로 결정했고, 산업보건 의뢰를 통해 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 처리하겠다고 말해 놓은 예정된 회신 전화, 작업지시서, 기본적인 후속 조치들을 계속 잊어버려요. 회사에 일이 다 쌓여 버려서, 승진 기회를 놓칠 수도 있다고 해서 여기로 보내졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 건망증이나 정리정돈 문제를 언제부터 겪기 시작하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 솔직히 초등학교 때부터요. 선생님들이 제가 똑똑하다고 하시면서도, 늘 서류를 잃어버리고, 지시사항의 일부를 놓치고, 수업 과제를 끝내려면 계속 알려줘야 했어요. 이건 지금 이 직장의 압박이 있기 훨씬 전부터 그랬어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 몸이 자주 안절부절못하거나 계속 꼼지락거리고 가만히 앉아 있기 힘든 느낌이 자주 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 안절부절못하거나 가만히 앉아 있지 못한다고 느낀 적은 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 주변에서 일어나는 일들 때문에 쉽게 주의가 흐트러지는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 디지털 작업지시서를 읽다가, 절반쯤 읽었을 때 어떤 소리나 다른 작업 때문에 정신이 팔려요. 그러면 방금 읽은 내용이 뭔지도 모르겠다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 아만다가 속한 시설관리 부서는 새로운 운영 관리 업체가 디지털 작업지시서와 에너지 효율 감사, 그리고 그녀가 기대하던 선임 시설관리직 승진과 연계된 한층 엄격한 문서 기준을 도입하면서 큰 변화를 겪었다. 이후 11개월 동안, 오랫동안 의존해 온 손으로 작성한 체크리스트와 물리적인 업무 루틴만으로는 더 이상 충분하지 않았다. 그녀는 여러 단계로 이루어진 서비스 요청 중 집중력을 유지하는 데 어려움을 겪었고, 작업에 필요한 공구와 태블릿을 잃어버렸으며, 예정된 회신 전화를 잊어버리고, 지시사항을 이해했음에도 불구하고 여러 유지보수 업무를 끝맺지 못한 채 남겨두었다. 그 결과로 생긴 업무 적체와 입주민들의 불만, 그리고 아차 사고 이후 진행된 공식 안전 검토는 이 문제를 단순한 직장 내 압박으로 치부할 수 없게 만들었다. 그녀는 오랫동안 노력해 온 승진의 길을 포기하는 대신 평가를 받기로 결정했고, 산업보건 의뢰를 통해 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S002 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - S003 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
+  - S004 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - S007 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.
+  - S009 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
-  누락: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.
+  - 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).
+  - 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S003_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S003_P002__gemini-3.8-flash_kor.xlsx
@@ -649,6 +649,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -692,11 +697,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S003_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S003_P002__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.8334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.9167</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
